--- a/Data/Excel/tower.xlsx
+++ b/Data/Excel/tower.xlsx
@@ -213,19 +213,19 @@
     <t>iconLocation</t>
   </si>
   <si>
-    <t>ui_td_tower_arrow_icon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ui_td_tower_fire_icon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ui_td_tower_ice_icon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ui_td_tower_cannon_icon</t>
+    <t>Assets/Arts/UI/TowerDefense/Icons/Towers/ui_td_tower_arrow_icon.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/TowerDefense/Icons/Towers/ui_td_tower_fire_icon.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/TowerDefense/Icons/Towers/ui_td_tower_ice_icon.png</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Arts/UI/TowerDefense/Icons/Towers/ui_td_tower_cannon_icon.png</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>

--- a/Data/Excel/tower.xlsx
+++ b/Data/Excel/tower.xlsx
@@ -725,7 +725,7 @@
     <row r="5" spans="1:19" ht="27.95" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
-        <v>1001</v>
+        <v>30100001</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>28</v>
@@ -740,7 +740,7 @@
         <v>39</v>
       </c>
       <c r="G5" s="2">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="H5" s="2">
         <v>100</v>
@@ -782,7 +782,7 @@
     <row r="6" spans="1:19" ht="27.95" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
-        <v>1002</v>
+        <v>30100002</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>41</v>
@@ -797,7 +797,7 @@
         <v>32</v>
       </c>
       <c r="G6" s="2">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="H6" s="2">
         <v>180</v>
@@ -839,7 +839,7 @@
     <row r="7" spans="1:19" ht="24" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
-        <v>1003</v>
+        <v>30100003</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>40</v>
@@ -854,7 +854,7 @@
         <v>32</v>
       </c>
       <c r="G7" s="2">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="H7" s="2">
         <v>150</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="8" spans="1:19">
       <c r="B8" s="2">
-        <v>1004</v>
+        <v>30100004</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>42</v>
@@ -910,7 +910,7 @@
         <v>32</v>
       </c>
       <c r="G8" s="2">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="H8" s="2">
         <v>150</v>
@@ -951,7 +951,7 @@
     </row>
     <row r="9" spans="1:19">
       <c r="B9" s="2">
-        <v>1005</v>
+        <v>30100005</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>43</v>
@@ -966,7 +966,7 @@
         <v>32</v>
       </c>
       <c r="G9" s="2">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="H9" s="2">
         <v>150</v>
